--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF42BCE-ABC1-4FA8-86F5-F2DC6A448690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95AA4A2E-14F8-40BA-ACCA-98595DBF08CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{5CC9697C-BEBF-454C-9830-8930A9F64DCB}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{5CC9697C-BEBF-454C-9830-8930A9F64DCB}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -312,13 +312,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -407,34 +413,37 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -798,7 +807,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3">
-        <v>283.95999999999998</v>
+        <v>307.5</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -809,10 +818,10 @@
         <v>5</v>
       </c>
       <c r="H4" s="4">
-        <v>14687.356</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>85</v>
+        <v>14594.18</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -824,7 +833,7 @@
       </c>
       <c r="H5" s="4">
         <f>H3*H4</f>
-        <v>4170621.6097599994</v>
+        <v>4487710.3499999996</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -832,11 +841,11 @@
         <v>7</v>
       </c>
       <c r="H6" s="4">
-        <f>45572+22935</f>
-        <v>68507</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>85</v>
+        <f>39544+22855</f>
+        <v>62399</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -850,11 +859,11 @@
         <v>8</v>
       </c>
       <c r="H7" s="4">
-        <f>74404+8310</f>
-        <v>82714</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>85</v>
+        <f>11007+71340</f>
+        <v>82347</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -863,7 +872,7 @@
       </c>
       <c r="H8" s="4">
         <f>H5-H6+H7</f>
-        <v>4184828.6097599994</v>
+        <v>4507658.3499999996</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -1014,7 +1023,9 @@
       <c r="P3" s="4">
         <v>56994</v>
       </c>
-      <c r="Q3" s="4"/>
+      <c r="Q3" s="4">
+        <v>54252</v>
+      </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -1137,7 +1148,9 @@
       <c r="P4" s="4">
         <v>8399</v>
       </c>
-      <c r="Q4" s="4"/>
+      <c r="Q4" s="4">
+        <v>10352</v>
+      </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
@@ -1260,7 +1273,9 @@
       <c r="P5" s="4">
         <v>6914</v>
       </c>
-      <c r="Q5" s="4"/>
+      <c r="Q5" s="4">
+        <v>6191</v>
+      </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
@@ -1383,7 +1398,9 @@
       <c r="P6" s="4">
         <v>7901</v>
       </c>
-      <c r="Q6" s="4"/>
+      <c r="Q6" s="4">
+        <v>7833</v>
+      </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
@@ -1506,7 +1523,9 @@
       <c r="P7" s="4">
         <v>80208</v>
       </c>
-      <c r="Q7" s="4"/>
+      <c r="Q7" s="4">
+        <v>78678</v>
+      </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
@@ -1632,7 +1651,9 @@
       <c r="P8" s="4">
         <v>30976</v>
       </c>
-      <c r="Q8" s="4"/>
+      <c r="Q8" s="4">
+        <v>30739</v>
+      </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
@@ -1746,7 +1767,7 @@
         <v>85777</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" ref="J9:P9" si="3">J7+J8</f>
+        <f t="shared" ref="J9:Q9" si="3">J7+J8</f>
         <v>94930</v>
       </c>
       <c r="K9" s="9">
@@ -1773,7 +1794,10 @@
         <f t="shared" si="3"/>
         <v>111184</v>
       </c>
-      <c r="Q9" s="9"/>
+      <c r="Q9" s="9">
+        <f t="shared" si="3"/>
+        <v>109417</v>
+      </c>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
       <c r="T9" s="4"/>
@@ -1912,7 +1936,9 @@
       <c r="P10" s="4">
         <v>49179</v>
       </c>
-      <c r="Q10" s="4"/>
+      <c r="Q10" s="4">
+        <v>47153</v>
+      </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
@@ -2035,7 +2061,9 @@
       <c r="P11" s="4">
         <v>7224</v>
       </c>
-      <c r="Q11" s="4"/>
+      <c r="Q11" s="4">
+        <v>7494</v>
+      </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
@@ -2153,7 +2181,7 @@
         <v>43879</v>
       </c>
       <c r="K12" s="4">
-        <f t="shared" ref="K12:P12" si="6">K9-SUM(K10:K11)</f>
+        <f t="shared" ref="K12:Q12" si="6">K9-SUM(K10:K11)</f>
         <v>58275</v>
       </c>
       <c r="L12" s="4">
@@ -2176,7 +2204,10 @@
         <f t="shared" si="6"/>
         <v>54781</v>
       </c>
-      <c r="Q12" s="4"/>
+      <c r="Q12" s="4">
+        <f t="shared" si="6"/>
+        <v>54770</v>
+      </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
@@ -2315,7 +2346,9 @@
       <c r="P13" s="4">
         <v>11419</v>
       </c>
-      <c r="Q13" s="4"/>
+      <c r="Q13" s="4">
+        <v>11729</v>
+      </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
@@ -2438,7 +2471,9 @@
       <c r="P14" s="4">
         <v>7477</v>
       </c>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="4">
+        <v>7346</v>
+      </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
@@ -2556,7 +2591,7 @@
         <v>29591</v>
       </c>
       <c r="K15" s="4">
-        <f t="shared" ref="K15:P15" si="9">K12-SUM(K13:K14)</f>
+        <f t="shared" ref="K15:Q15" si="9">K12-SUM(K13:K14)</f>
         <v>42832</v>
       </c>
       <c r="L15" s="4">
@@ -2579,7 +2614,10 @@
         <f t="shared" si="9"/>
         <v>35885</v>
       </c>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="4">
+        <f t="shared" si="9"/>
+        <v>35695</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
@@ -2718,7 +2756,9 @@
       <c r="P16" s="4">
         <v>-52</v>
       </c>
-      <c r="Q16" s="4"/>
+      <c r="Q16" s="4">
+        <v>572</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
@@ -2836,7 +2876,7 @@
         <v>29610</v>
       </c>
       <c r="K17" s="4">
-        <f t="shared" ref="K17:P17" si="12">K15+K16</f>
+        <f t="shared" ref="K17:Q17" si="12">K15+K16</f>
         <v>42584</v>
       </c>
       <c r="L17" s="4">
@@ -2859,7 +2899,10 @@
         <f t="shared" si="12"/>
         <v>35833</v>
       </c>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="4">
+        <f t="shared" si="12"/>
+        <v>36267</v>
+      </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
@@ -2998,7 +3041,9 @@
       <c r="P18" s="4">
         <v>6255</v>
       </c>
-      <c r="Q18" s="4"/>
+      <c r="Q18" s="4">
+        <v>6478</v>
+      </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
@@ -3139,7 +3184,10 @@
         <f t="shared" si="15"/>
         <v>29578</v>
       </c>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="4">
+        <f t="shared" si="15"/>
+        <v>29789</v>
+      </c>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
@@ -3385,7 +3433,10 @@
         <f t="shared" si="17"/>
         <v>2.0157731626157425</v>
       </c>
-      <c r="Q21" s="10"/>
+      <c r="Q21" s="10">
+        <f t="shared" si="17"/>
+        <v>2.0325311423017429</v>
+      </c>
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
       <c r="T21" s="4"/>
@@ -3524,7 +3575,9 @@
       <c r="P22" s="4">
         <v>14673.278</v>
       </c>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="4">
+        <v>14656.11</v>
+      </c>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
@@ -3715,7 +3768,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="11">
-        <f t="shared" ref="K24:P27" si="19">K3/G3-1</f>
+        <f t="shared" ref="K24:Q27" si="19">K3/G3-1</f>
         <v>-8.0915899113368495E-3</v>
       </c>
       <c r="L24" s="11">
@@ -3738,7 +3791,10 @@
         <f t="shared" si="19"/>
         <v>0.21675455263551169</v>
       </c>
-      <c r="Q24" s="11"/>
+      <c r="Q24" s="11">
+        <f t="shared" si="19"/>
+        <v>0.2169036831008031</v>
+      </c>
       <c r="R24" s="11"/>
       <c r="S24" s="11"/>
       <c r="T24" s="11"/>
@@ -3817,7 +3873,10 @@
         <f t="shared" si="19"/>
         <v>5.661089445213241E-2</v>
       </c>
-      <c r="Q25" s="11"/>
+      <c r="Q25" s="11">
+        <f t="shared" si="19"/>
+        <v>0.28660203827989061</v>
+      </c>
       <c r="R25" s="11"/>
       <c r="S25" s="11"/>
       <c r="T25" s="11"/>
@@ -3896,7 +3955,10 @@
         <f t="shared" si="19"/>
         <v>7.9975007810059395E-2</v>
       </c>
-      <c r="Q26" s="11"/>
+      <c r="Q26" s="11">
+        <f t="shared" si="19"/>
+        <v>-5.9261510408752494E-2</v>
+      </c>
       <c r="R26" s="11"/>
       <c r="S26" s="11"/>
       <c r="T26" s="11"/>
@@ -3975,7 +4037,10 @@
         <f t="shared" si="19"/>
         <v>5.0385535761765521E-2</v>
       </c>
-      <c r="Q27" s="11"/>
+      <c r="Q27" s="11">
+        <f t="shared" si="19"/>
+        <v>5.7941653160453743E-2</v>
+      </c>
       <c r="R27" s="11"/>
       <c r="S27" s="11"/>
       <c r="T27" s="11"/>
@@ -4031,7 +4096,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K28" s="11">
-        <f t="shared" ref="K28:P28" si="24">K8/G8-1</f>
+        <f t="shared" ref="K28:Q28" si="24">K8/G8-1</f>
         <v>0.13942120517368162</v>
       </c>
       <c r="L28" s="11">
@@ -4054,7 +4119,10 @@
         <f t="shared" si="24"/>
         <v>0.16254456746106216</v>
       </c>
-      <c r="Q28" s="11"/>
+      <c r="Q28" s="11">
+        <f t="shared" si="24"/>
+        <v>0.12092039528862641</v>
+      </c>
       <c r="R28" s="11"/>
       <c r="S28" s="11"/>
       <c r="T28" s="11"/>
@@ -4110,7 +4178,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K29" s="12">
-        <f t="shared" ref="K29:P29" si="26">K9/G9-1</f>
+        <f t="shared" ref="K29:Q29" si="26">K9/G9-1</f>
         <v>3.9514948776918191E-2</v>
       </c>
       <c r="L29" s="12">
@@ -4133,7 +4201,10 @@
         <f t="shared" si="26"/>
         <v>0.16595182415922993</v>
       </c>
-      <c r="Q29" s="12"/>
+      <c r="Q29" s="12">
+        <f t="shared" si="26"/>
+        <v>0.16356501765281384</v>
+      </c>
       <c r="R29" s="12"/>
       <c r="S29" s="12"/>
       <c r="T29" s="12"/>
@@ -4227,37 +4298,40 @@
         <f t="shared" si="30"/>
         <v>0.4927057850050367</v>
       </c>
-      <c r="Q30" s="11"/>
+      <c r="Q30" s="11">
+        <f t="shared" ref="Q30" si="31">Q12/Q9</f>
+        <v>0.50056206987945195</v>
+      </c>
       <c r="R30" s="11"/>
       <c r="S30" s="11"/>
       <c r="T30" s="11"/>
       <c r="U30" s="4"/>
       <c r="V30" s="11" t="e">
-        <f t="shared" ref="V30:AB30" si="31">V12/V9</f>
+        <f t="shared" ref="V30:AB30" si="32">V12/V9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="W30" s="11" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X30" s="11" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y30" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.43309630561360085</v>
       </c>
       <c r="Z30" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.44131129577207562</v>
       </c>
       <c r="AA30" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.46206349815233932</v>
       </c>
       <c r="AB30" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.46905164107160452</v>
       </c>
     </row>
@@ -4266,27 +4340,27 @@
         <v>53</v>
       </c>
       <c r="C31" s="11" t="e">
-        <f t="shared" ref="C31:H31" si="32">C15/C9</f>
+        <f t="shared" ref="C31:H31" si="33">C15/C9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D31" s="11" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E31" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.28115945572576012</v>
       </c>
       <c r="F31" s="11" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G31" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.33763746602550698</v>
       </c>
       <c r="H31" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.30742785362467356</v>
       </c>
       <c r="I31" s="11">
@@ -4298,60 +4372,63 @@
         <v>0.31171389444854103</v>
       </c>
       <c r="K31" s="11">
-        <f t="shared" ref="K31:N31" si="33">K15/K9</f>
+        <f t="shared" ref="K31:N31" si="34">K15/K9</f>
         <v>0.34458567980691873</v>
       </c>
       <c r="L31" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.31029058610094484</v>
       </c>
       <c r="M31" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.29990641881832492</v>
       </c>
       <c r="N31" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.31646594968086977</v>
       </c>
       <c r="O31" s="11">
-        <f t="shared" ref="O31:P31" si="34">O15/O9</f>
+        <f t="shared" ref="O31:P31" si="35">O15/O9</f>
         <v>0.35373827875010433</v>
       </c>
       <c r="P31" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.32275327385235286</v>
       </c>
-      <c r="Q31" s="11"/>
+      <c r="Q31" s="11">
+        <f t="shared" ref="Q31" si="36">Q15/Q9</f>
+        <v>0.3262290137729969</v>
+      </c>
       <c r="R31" s="11"/>
       <c r="S31" s="11"/>
       <c r="T31" s="11"/>
       <c r="U31" s="4"/>
       <c r="V31" s="11" t="e">
-        <f t="shared" ref="V31:AB31" si="35">V15/V9</f>
+        <f t="shared" ref="V31:AB31" si="37">V15/V9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="W31" s="11" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X31" s="11" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y31" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.30288744395528594</v>
       </c>
       <c r="Z31" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.29821412265024722</v>
       </c>
       <c r="AA31" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.31510222870075566</v>
       </c>
       <c r="AB31" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.31970799762591884</v>
       </c>
     </row>
@@ -4360,27 +4437,27 @@
         <v>54</v>
       </c>
       <c r="C32" s="11" t="e">
-        <f t="shared" ref="C32:H32" si="36">C18/C17</f>
+        <f t="shared" ref="C32:H32" si="38">C18/C17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D32" s="11" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E32" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.12545638499098227</v>
       </c>
       <c r="F32" s="11" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G32" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.15889194752374575</v>
       </c>
       <c r="H32" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.1576021099151757</v>
       </c>
       <c r="I32" s="11">
@@ -4392,60 +4469,63 @@
         <v>0.50233029381965555</v>
       </c>
       <c r="K32" s="11">
-        <f t="shared" ref="K32:N32" si="37">K18/K17</f>
+        <f t="shared" ref="K32:N32" si="39">K18/K17</f>
         <v>0.14686267142588766</v>
       </c>
       <c r="L32" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0.15455475946775846</v>
       </c>
       <c r="M32" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0.16399700331775535</v>
       </c>
       <c r="N32" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0.16272405804170223</v>
       </c>
       <c r="O32" s="11">
-        <f t="shared" ref="O32:P32" si="38">O18/O17</f>
+        <f t="shared" ref="O32:P32" si="40">O18/O17</f>
         <v>0.17460099603937101</v>
       </c>
       <c r="P32" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.17455976334663578</v>
       </c>
-      <c r="Q32" s="11"/>
+      <c r="Q32" s="11">
+        <f t="shared" ref="Q32" si="41">Q18/Q17</f>
+        <v>0.17861968180439519</v>
+      </c>
       <c r="R32" s="11"/>
       <c r="S32" s="11"/>
       <c r="T32" s="11"/>
       <c r="U32" s="4"/>
       <c r="V32" s="11" t="e">
-        <f t="shared" ref="V32:AB32" si="39">V18/V17</f>
+        <f t="shared" ref="V32:AB32" si="42">V18/V17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="W32" s="11" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X32" s="11" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y32" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.16204461684424407</v>
       </c>
       <c r="Z32" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.14719174228036858</v>
       </c>
       <c r="AA32" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.24091185164189982</v>
       </c>
       <c r="AB32" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.15610002335586043</v>
       </c>
     </row>
@@ -4709,11 +4789,11 @@
         <v>61</v>
       </c>
       <c r="C40" s="4">
-        <f t="shared" ref="C40:H40" si="40">SUM(C34:C39)</f>
+        <f t="shared" ref="C40:H40" si="43">SUM(C34:C39)</f>
         <v>0</v>
       </c>
       <c r="D40" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="E40" s="4">
@@ -4721,15 +4801,15 @@
         <v>143566</v>
       </c>
       <c r="F40" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="G40" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="H40" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>152987</v>
       </c>
       <c r="I40" s="4">
@@ -4880,27 +4960,27 @@
         <v>63</v>
       </c>
       <c r="C44" s="4">
-        <f t="shared" ref="C44:H44" si="41">SUM(C41:C43)</f>
+        <f t="shared" ref="C44:H44" si="44">SUM(C41:C43)</f>
         <v>0</v>
       </c>
       <c r="D44" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>209017</v>
       </c>
       <c r="F44" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="G44" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="H44" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>211993</v>
       </c>
       <c r="I44" s="4">
@@ -4908,15 +4988,15 @@
         <v>206177</v>
       </c>
       <c r="J44" s="4">
-        <f t="shared" ref="J44:L44" si="42">SUM(J41:J43)</f>
+        <f t="shared" ref="J44:L44" si="45">SUM(J41:J43)</f>
         <v>0</v>
       </c>
       <c r="K44" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L44" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>212559</v>
       </c>
       <c r="M44" s="4"/>
@@ -4940,43 +5020,43 @@
         <v>64</v>
       </c>
       <c r="C45" s="9">
-        <f t="shared" ref="C45:I45" si="43">C44+C40</f>
+        <f t="shared" ref="C45:I45" si="46">C44+C40</f>
         <v>0</v>
       </c>
       <c r="D45" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E45" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>352583</v>
       </c>
       <c r="F45" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="G45" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="H45" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>364980</v>
       </c>
       <c r="I45" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>331612</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" ref="J45:L45" si="44">J44+J40</f>
+        <f t="shared" ref="J45:L45" si="47">J44+J40</f>
         <v>0</v>
       </c>
       <c r="K45" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="L45" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>331233</v>
       </c>
       <c r="M45" s="4"/>
@@ -5190,27 +5270,27 @@
         <v>73</v>
       </c>
       <c r="C51" s="4">
-        <f t="shared" ref="C51:H51" si="45">SUM(C46:C50)</f>
+        <f t="shared" ref="C51:H51" si="48">SUM(C46:C50)</f>
         <v>0</v>
       </c>
       <c r="D51" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>145308</v>
       </c>
       <c r="F51" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G51" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="H51" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>176392</v>
       </c>
       <c r="I51" s="4">
@@ -5218,15 +5298,15 @@
         <v>131624</v>
       </c>
       <c r="J51" s="4">
-        <f t="shared" ref="J51:L51" si="46">SUM(J46:J50)</f>
+        <f t="shared" ref="J51:L51" si="49">SUM(J46:J50)</f>
         <v>0</v>
       </c>
       <c r="K51" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="L51" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>144571</v>
       </c>
       <c r="M51" s="4"/>
@@ -5326,27 +5406,27 @@
         <v>69</v>
       </c>
       <c r="C54" s="4">
-        <f t="shared" ref="C54:H54" si="47">SUM(C52:C53)</f>
+        <f t="shared" ref="C54:H54" si="50">SUM(C52:C53)</f>
         <v>0</v>
       </c>
       <c r="D54" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>145129</v>
       </c>
       <c r="F54" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="G54" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="H54" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>131638</v>
       </c>
       <c r="I54" s="4">
@@ -5383,40 +5463,40 @@
         <v>70</v>
       </c>
       <c r="C55" s="9">
-        <f t="shared" ref="C55:I55" si="48">C54+C51</f>
+        <f t="shared" ref="C55:I55" si="51">C54+C51</f>
         <v>0</v>
       </c>
       <c r="D55" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="E55" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>290437</v>
       </c>
       <c r="F55" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="G55" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="H55" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>308030</v>
       </c>
       <c r="I55" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>264904</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="9">
-        <f t="shared" ref="K55:L55" si="49">K54+K51</f>
+        <f t="shared" ref="K55:L55" si="52">K54+K51</f>
         <v>0</v>
       </c>
       <c r="L55" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>264437</v>
       </c>
       <c r="M55" s="4"/>
@@ -5478,43 +5558,43 @@
         <v>72</v>
       </c>
       <c r="C57" s="9">
-        <f t="shared" ref="C57:I57" si="50">C55+C56</f>
+        <f t="shared" ref="C57:I57" si="53">C55+C56</f>
         <v>0</v>
       </c>
       <c r="D57" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="E57" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>352583</v>
       </c>
       <c r="F57" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="G57" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H57" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>364980</v>
       </c>
       <c r="I57" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>331612</v>
       </c>
       <c r="J57" s="9">
-        <f t="shared" ref="J57:L57" si="51">J55+J56</f>
+        <f t="shared" ref="J57:L57" si="54">J55+J56</f>
         <v>0</v>
       </c>
       <c r="K57" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L57" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>331233</v>
       </c>
       <c r="M57" s="4"/>
@@ -5615,7 +5695,9 @@
       <c r="P60" s="4">
         <v>82627</v>
       </c>
-      <c r="Q60" s="4"/>
+      <c r="Q60" s="4">
+        <v>116996</v>
+      </c>
       <c r="R60" s="4"/>
       <c r="S60" s="4"/>
       <c r="T60" s="4"/>
@@ -5655,7 +5737,9 @@
       <c r="P61" s="4">
         <v>-4344</v>
       </c>
-      <c r="Q61" s="4"/>
+      <c r="Q61" s="4">
+        <v>-6799</v>
+      </c>
       <c r="R61" s="4"/>
       <c r="S61" s="4"/>
       <c r="T61" s="4"/>
@@ -5672,27 +5756,27 @@
         <v>76</v>
       </c>
       <c r="C62" s="4">
-        <f t="shared" ref="C62" si="52">C60-C61</f>
+        <f t="shared" ref="C62" si="55">C60-C61</f>
         <v>0</v>
       </c>
       <c r="D62" s="4">
-        <f t="shared" ref="D62:H62" si="53">+D60+D61</f>
+        <f t="shared" ref="D62:H62" si="56">+D60+D61</f>
         <v>0</v>
       </c>
       <c r="E62" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>80149</v>
       </c>
       <c r="F62" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="G62" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="H62" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>58197</v>
       </c>
       <c r="I62" s="4">
@@ -5700,25 +5784,28 @@
         <v>84904</v>
       </c>
       <c r="J62" s="4">
-        <f t="shared" ref="J62:L62" si="54">+J60+J61</f>
+        <f t="shared" ref="J62:L62" si="57">+J60+J61</f>
         <v>0</v>
       </c>
       <c r="K62" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="L62" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>47876</v>
       </c>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
       <c r="P62" s="4">
-        <f t="shared" ref="P62" si="55">+P60+P61</f>
+        <f t="shared" ref="P62:Q62" si="58">+P60+P61</f>
         <v>78283</v>
       </c>
-      <c r="Q62" s="4"/>
+      <c r="Q62" s="4">
+        <f t="shared" si="58"/>
+        <v>110197</v>
+      </c>
       <c r="R62" s="4"/>
       <c r="S62" s="4"/>
       <c r="T62" s="4"/>
